--- a/data/trans_bre/IP18A02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 5,07</t>
+          <t>-16,89; 5,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 12,17</t>
+          <t>-7,03; 11,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 10,74</t>
+          <t>-9,38; 10,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 28,65</t>
+          <t>-18,87; 28,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,28; 11,73</t>
+          <t>-32,9; 12,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 37,02</t>
+          <t>-15,66; 34,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 29,43</t>
+          <t>-18,84; 28,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 95,52</t>
+          <t>-37,41; 91,63</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 12,1</t>
+          <t>-0,12; 11,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 9,93</t>
+          <t>-3,27; 8,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 2,83</t>
+          <t>-9,58; 2,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 13,03</t>
+          <t>-16,86; 12,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 67,42</t>
+          <t>-2,01; 65,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 64,11</t>
+          <t>-14,77; 57,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 17,03</t>
+          <t>-41,28; 14,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,95; 206,61</t>
+          <t>-75,61; 169,26</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 13,57</t>
+          <t>-2,74; 12,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 7,96</t>
+          <t>-5,68; 7,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 9,94</t>
+          <t>-1,37; 10,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 12,19</t>
+          <t>-15,69; 12,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 133,22</t>
+          <t>-17,1; 119,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 85,88</t>
+          <t>-35,28; 78,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 150,61</t>
+          <t>-12,56; 153,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-78,97; 245,96</t>
+          <t>-83,8; 224,43</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 8,35</t>
+          <t>-1,66; 8,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 6,69</t>
+          <t>-5,1; 6,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 0,31</t>
+          <t>-9,82; 0,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 19,53</t>
+          <t>-16,39; 17,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 204,24</t>
+          <t>-18,02; 182,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,21; 100,75</t>
+          <t>-42,36; 100,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,16; 5,83</t>
+          <t>-72,4; 8,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,4; 235,89</t>
+          <t>-71,56; 171,93</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 6,81</t>
+          <t>-0,7; 6,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 5,5</t>
+          <t>-1,39; 6,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 3,25</t>
+          <t>-3,93; 2,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 10,24</t>
+          <t>-8,02; 8,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 38,51</t>
+          <t>-3,08; 37,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 32,42</t>
+          <t>-6,93; 35,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 19,2</t>
+          <t>-18,51; 15,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 69,03</t>
+          <t>-35,03; 56,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 5,15</t>
+          <t>-17,35; 4,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 11,65</t>
+          <t>-6,49; 12,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 10,91</t>
+          <t>-9,41; 10,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 28,61</t>
+          <t>-18,84; 29,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,9; 12,17</t>
+          <t>-32,71; 10,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 34,67</t>
+          <t>-15,84; 36,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 28,1</t>
+          <t>-19,46; 26,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,41; 91,63</t>
+          <t>-35,98; 102,46</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 11,84</t>
+          <t>-0,57; 12,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 8,7</t>
+          <t>-3,59; 8,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 2,49</t>
+          <t>-9,86; 3,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 12,74</t>
+          <t>-16,15; 12,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 65,72</t>
+          <t>-3,64; 71,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 57,67</t>
+          <t>-16,55; 52,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 14,52</t>
+          <t>-41,52; 21,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,61; 169,26</t>
+          <t>-78,0; 190,46</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 12,37</t>
+          <t>-2,69; 13,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 7,48</t>
+          <t>-4,64; 7,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 10,24</t>
+          <t>-1,02; 10,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 12,49</t>
+          <t>-13,51; 13,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 119,4</t>
+          <t>-19,47; 131,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,28; 78,06</t>
+          <t>-29,77; 82,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 153,09</t>
+          <t>-8,8; 161,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-83,8; 224,43</t>
+          <t>-78,25; 396,15</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 8,22</t>
+          <t>-2,23; 7,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 6,5</t>
+          <t>-4,83; 6,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 0,38</t>
+          <t>-9,6; 0,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 17,43</t>
+          <t>-16,49; 19,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 182,01</t>
+          <t>-26,89; 158,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,36; 100,32</t>
+          <t>-40,44; 100,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,4; 8,24</t>
+          <t>-73,33; 8,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,56; 171,93</t>
+          <t>-71,53; 186,93</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,9</t>
+          <t>-0,79; 6,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 6,12</t>
+          <t>-1,48; 5,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,79</t>
+          <t>-3,76; 3,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 8,7</t>
+          <t>-8,11; 9,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 37,04</t>
+          <t>-3,61; 37,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 35,59</t>
+          <t>-7,33; 34,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 15,8</t>
+          <t>-17,62; 19,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 56,66</t>
+          <t>-36,46; 62,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,62</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 4,29</t>
+          <t>-15,99; 5,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 12,03</t>
+          <t>-6,59; 12,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 10,37</t>
+          <t>-9,43; 10,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 29,13</t>
+          <t>-19,23; 29,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 10,84</t>
+          <t>-31,28; 11,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 36,09</t>
+          <t>-15,39; 37,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,46; 26,98</t>
+          <t>-19,33; 29,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 102,46</t>
+          <t>-35,72; 95,87</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-15,08%</t>
+          <t>-7,89%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 12,32</t>
+          <t>0,18; 12,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 8,31</t>
+          <t>-2,79; 9,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 3,35</t>
+          <t>-8,92; 2,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 12,84</t>
+          <t>-14,99; 14,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 71,93</t>
+          <t>0,18; 67,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 52,78</t>
+          <t>-14,45; 64,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,52; 21,09</t>
+          <t>-38,08; 17,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,0; 190,46</t>
+          <t>-70,46; 209,47</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-8,31%</t>
+          <t>-5,75%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 13,95</t>
+          <t>-2,59; 13,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 7,37</t>
+          <t>-5,35; 7,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,3</t>
+          <t>-1,19; 9,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 13,66</t>
+          <t>-14,86; 13,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 131,53</t>
+          <t>-15,54; 133,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 82,57</t>
+          <t>-34,15; 85,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 161,4</t>
+          <t>-14,17; 150,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 396,15</t>
+          <t>-79,37; 252,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 7,6</t>
+          <t>-1,95; 8,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 6,21</t>
+          <t>-4,49; 6,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 0,66</t>
+          <t>-9,91; 0,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 19,94</t>
+          <t>-14,92; 21,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 158,58</t>
+          <t>-21,37; 204,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 100,44</t>
+          <t>-37,21; 100,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,33; 8,63</t>
+          <t>-72,16; 5,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,53; 186,93</t>
+          <t>-64,35; 244,25</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 6,88</t>
+          <t>-0,4; 6,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 5,81</t>
+          <t>-1,41; 5,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,35</t>
+          <t>-4,07; 3,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 9,13</t>
+          <t>-7,7; 11,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 37,26</t>
+          <t>-1,47; 38,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 34,29</t>
+          <t>-6,74; 32,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 19,01</t>
+          <t>-18,97; 19,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 62,63</t>
+          <t>-32,43; 79,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-6,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,43</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-12,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-6.001826171816776</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.749293150380066</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.7146573021216795</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5.434649413005732</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.126331877384176</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.07254901932929737</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.01627410759760154</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1276585260888873</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-15,99; 5,07</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,59; 12,17</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-9,43; 10,74</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-19,23; 29,96</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-31,28; 11,73</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-15,39; 37,02</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-19,33; 29,43</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-35,72; 95,87</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-15.99034460693687</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.592050972900607</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-9.433578522574175</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-19.23107186295639</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3127524043661817</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1539235288651448</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1933064500602389</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3571761012036894</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.066753530529971</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.16646308288951</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.74053835890168</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>29.96259061061294</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1173042238001205</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3701597993008137</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.294347548843965</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.9587082997620086</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,96</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,85</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,25</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>28,91%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,72%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-15,94%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-7,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 12,1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,79; 9,93</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-8,92; 2,83</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-14,99; 14,78</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 67,42</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-14,45; 64,11</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-38,08; 17,03</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-70,46; 209,47</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>5.962394237878704</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.852753072381553</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-3.245390997215172</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.194202478906994</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2891183954631552</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.157228617719555</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1594474293125627</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.07891672710672819</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,4</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36,82%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>47,07%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-5,75%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1801450849073623</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.789818211640092</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-8.924655076110868</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-14.99293509401275</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.001808925504591237</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1444628345430859</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3807991909202134</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7046461595828696</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,59; 13,57</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,35; 7,96</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,19; 9,94</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-14,86; 13,54</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-15,54; 133,22</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-34,15; 85,88</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-14,17; 150,61</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-79,37; 252,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>12.10017731439013</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.92896826266931</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.825121706197206</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>14.77546269386919</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.6742186738834132</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.6411014727282748</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.1703485563462836</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.094735593898759</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,22</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-4,61</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>47,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-43,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.071785109129879</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.379438708984511</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.402775232885461</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.7645383366945868</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.3682357042435627</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.1105691958552919</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.4707123442362182</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.05752443208032576</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,95; 8,35</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,49; 6,69</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-9,91; 0,31</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-14,92; 21,33</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-21,37; 204,24</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-37,21; 100,75</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-72,16; 5,83</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-64,35; 244,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.588062957156458</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.351094179392135</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.190361066341196</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-14.85748923418714</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1553880216549897</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3415485832309876</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1416696645371779</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7936867916816656</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>13.56735556335352</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.962049322398665</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.938653430009614</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>13.54247559681075</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.33222717240632</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.858836357850298</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.506062656571268</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.520226490539621</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3.221428435407895</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8398622630776578</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-4.609740093679466</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.7676319834676121</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.4750450878177424</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.08930106225747794</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.4397743381864539</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.04052083484484588</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.947558573854608</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.486912858924184</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-9.907898855662802</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-14.92235040467586</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2136586085726581</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3720559165144287</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.7216009542610848</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6435307402863722</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.351430923549566</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.688106426824869</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.3110463815049918</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>21.32637451099389</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.042407078599334</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.007506736380222</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.05825134584137591</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.442481494783658</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,18</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-2,63%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 6,81</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,41; 5,5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-4,07; 3,25</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-7,7; 11,65</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-1,47; 38,51</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-6,74; 32,42</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-18,97; 19,2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-32,43; 79,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>3.067977181979411</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.179293623676071</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.5151060260099621</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.056856116247168</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1512625239699349</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1152679863217762</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.02633492532701259</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.05459059384139254</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.3954708645696635</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.411789704823051</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.070316105248943</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-7.700849886118738</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.0146858207406714</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.06741745496136373</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1897196751374538</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3242723249216224</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.805964192419419</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.50101839174121</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.247968513022306</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>11.64560670278817</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.3851342308483013</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3242313314796282</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.1920367156577792</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.7970117666297448</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
